--- a/Spine_Projects/01_input_data/01_input_raw/Products/egasoline/Model_Data_Base_egasoline.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/egasoline/Model_Data_Base_egasoline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/djh_eco_cbs_dk/Documents/Documents/GitHub/Nord_H2ub/Spine_Projects/01_input_data/01_input_raw/Products/egasoline/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\egasoline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{505DA5C3-9445-46B4-88E6-67A195B16402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{593FA13C-3695-4D7B-B03C-A3DCDC66FAB8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B265BC-E6FD-4EEB-AEFF-FC09A53A5F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="138">
   <si>
     <t>Unit</t>
   </si>
@@ -461,6 +461,33 @@
   </si>
   <si>
     <t>60h</t>
+  </si>
+  <si>
+    <t>solar_plant_node</t>
+  </si>
+  <si>
+    <t>wind_onshore_plant_node</t>
+  </si>
+  <si>
+    <t>wind_offshore_plant_node</t>
+  </si>
+  <si>
+    <t>pl_wholesale_solar</t>
+  </si>
+  <si>
+    <t>pl_solar_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_onshore</t>
+  </si>
+  <si>
+    <t>pl_wind_onshore_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_offshore</t>
+  </si>
+  <si>
+    <t>pl_wind_offshore_PPA</t>
   </si>
 </sst>
 </file>
@@ -551,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -564,6 +591,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1343,8 +1372,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA5" totalsRowShown="0">
-  <autoFilter ref="A1:AA5" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
+  <autoFilter ref="A1:AA11" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{26B0CA71-1EA9-44CF-8E6D-31054ECA99A6}" name="Connection"/>
     <tableColumn id="26" xr3:uid="{E67F4435-EF76-417C-B715-53719E5FB41F}" name="Object_type"/>
@@ -1708,22 +1737,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" customWidth="1"/>
-    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1779,7 +1808,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1787,12 +1816,12 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -1800,12 +1829,12 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -1813,12 +1842,12 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -1840,7 +1869,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -1853,7 +1882,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -1870,7 +1899,7 @@
         <v>20.192799999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -1883,7 +1912,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -1899,7 +1928,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -1912,7 +1941,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -1925,7 +1954,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>116</v>
       </c>
@@ -1941,7 +1970,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>127</v>
       </c>
@@ -1954,7 +1983,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>125</v>
       </c>
@@ -1997,14 +2026,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" customWidth="1"/>
-    <col min="7" max="8" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="7" max="8" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2057,7 +2086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>69</v>
       </c>
@@ -2068,8 +2097,8 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
-        <v>70</v>
+      <c r="G2" t="s">
+        <v>129</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="7"/>
@@ -2082,7 +2111,7 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>102</v>
       </c>
@@ -2093,8 +2122,8 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>70</v>
+      <c r="G3" t="s">
+        <v>130</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -2107,7 +2136,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -2118,8 +2147,8 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>70</v>
+      <c r="G4" t="s">
+        <v>131</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2132,7 +2161,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>85</v>
       </c>
@@ -2167,7 +2196,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -2200,7 +2229,7 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -2237,7 +2266,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -2278,7 +2307,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -2311,7 +2340,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -2328,7 +2357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -2357,7 +2386,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>116</v>
       </c>
@@ -2404,7 +2433,7 @@
       </c>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>127</v>
       </c>
@@ -2433,7 +2462,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>125</v>
       </c>
@@ -2485,34 +2514,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="10.54296875" customWidth="1"/>
-    <col min="17" max="17" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.81640625" customWidth="1"/>
-    <col min="21" max="21" width="12.81640625" customWidth="1"/>
-    <col min="22" max="23" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="35.26953125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.85546875" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" customWidth="1"/>
+    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -2595,7 +2624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -2654,7 +2683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -2710,7 +2739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>121</v>
       </c>
@@ -2736,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -2771,6 +2800,297 @@
         <v>58</v>
       </c>
       <c r="AA5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>1000</v>
+      </c>
+      <c r="M6">
+        <v>1000</v>
+      </c>
+      <c r="N6">
+        <v>1000</v>
+      </c>
+      <c r="O6">
+        <v>1000</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>1000</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1000</v>
+      </c>
+      <c r="M7">
+        <v>1000</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>1000</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>1000</v>
+      </c>
+      <c r="M8">
+        <v>1000</v>
+      </c>
+      <c r="N8">
+        <v>1000</v>
+      </c>
+      <c r="O8">
+        <v>1000</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>1000</v>
+      </c>
+      <c r="M9">
+        <v>1000</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <v>1000</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>1000</v>
+      </c>
+      <c r="L10">
+        <v>1000</v>
+      </c>
+      <c r="M10">
+        <v>1000</v>
+      </c>
+      <c r="N10">
+        <v>1000</v>
+      </c>
+      <c r="O10">
+        <v>1000</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="L11">
+        <v>1000</v>
+      </c>
+      <c r="M11">
+        <v>1000</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA11">
         <v>1</v>
       </c>
     </row>
@@ -2799,22 +3119,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1796875" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -2849,7 +3169,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -2875,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -2924,127 +3244,127 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DC79B9-9C58-497E-9FD8-D3F2239E9BDC}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>119</v>
       </c>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/egasoline/Model_Data_Base_egasoline.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/egasoline/Model_Data_Base_egasoline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\egasoline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B265BC-E6FD-4EEB-AEFF-FC09A53A5F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C16C014-E571-4F49-BE2B-DFA7AED3CBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="137">
   <si>
     <t>Unit</t>
   </si>
@@ -337,12 +337,6 @@
     <t>initial_units_on</t>
   </si>
   <si>
-    <t>heat_low</t>
-  </si>
-  <si>
-    <t>heat_high</t>
-  </si>
-  <si>
     <t>Auxilliary</t>
   </si>
   <si>
@@ -457,9 +451,6 @@
     <t>co2_source</t>
   </si>
   <si>
-    <t>heat_recovery</t>
-  </si>
-  <si>
     <t>60h</t>
   </si>
   <si>
@@ -488,13 +479,19 @@
   </si>
   <si>
     <t>pl_wind_offshore_PPA</t>
+  </si>
+  <si>
+    <t>excess_heat</t>
+  </si>
+  <si>
+    <t>heat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +509,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -578,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -591,8 +595,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1319,8 +1322,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}" name="Table1" displayName="Table1" ref="A1:R14" totalsRowShown="0">
-  <autoFilter ref="A1:R14" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}" name="Table1" displayName="Table1" ref="A1:R13" totalsRowShown="0">
+  <autoFilter ref="A1:R13" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{C73E51D0-1842-42F3-9C00-F0DBD2E661BE}" name="Unit"/>
     <tableColumn id="40" xr3:uid="{C2CFC5A4-5329-4F74-926A-18CEB18C062C}" name="Object_type"/>
@@ -1346,8 +1349,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q14" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:Q14" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}" name="Table5" displayName="Table5" ref="A1:Q13" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:Q13" xr:uid="{C1664CC4-80CB-414D-BAFE-57FF9635D79F}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{2BE3E317-773B-4E82-9035-69A43C6CB21B}" name="Unit" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{22613EE0-390D-4B04-9A9B-6D5554D1C8ED}" name="Object_type" dataDxfId="18"/>
@@ -1736,20 +1739,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1760,7 +1770,7 @@
         <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
@@ -1769,16 +1779,16 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J1" t="s">
         <v>64</v>
@@ -1816,33 +1826,33 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1890,7 +1900,7 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>42</v>
@@ -1901,13 +1911,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1930,10 +1940,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
@@ -1943,10 +1953,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
         <v>82</v>
@@ -1956,50 +1966,37 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>88</v>
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P14" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P13" xr:uid="{D92CB468-B7A9-4082-9B81-D3B4634F286E}">
       <formula1>"h, D, W, M, Q, Y"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2025,12 +2022,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="7" max="8" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -2047,10 +2052,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>3</v>
@@ -2059,31 +2064,31 @@
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -2098,7 +2103,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="7"/>
@@ -2113,7 +2118,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>62</v>
@@ -2123,7 +2128,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -2138,7 +2143,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -2148,7 +2153,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2180,7 +2185,7 @@
         <v>78</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -2237,7 +2242,7 @@
         <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>78</v>
@@ -2245,10 +2250,10 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -2268,10 +2273,10 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>78</v>
@@ -2286,7 +2291,7 @@
         <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -2315,7 +2320,7 @@
         <v>45</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>75</v>
@@ -2342,13 +2347,13 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>75</v>
@@ -2359,13 +2364,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2388,10 +2393,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>78</v>
@@ -2400,21 +2405,19 @@
         <v>70</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>75</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>87</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="J12" s="3"/>
       <c r="K12" s="6">
         <v>42.75</v>
       </c>
@@ -2428,26 +2431,26 @@
       <c r="O12" s="6">
         <v>6.7340067340067344</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="8">
         <v>5.5096418732782366</v>
       </c>
       <c r="Q12" s="6"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>89</v>
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -2456,46 +2459,18 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4">
-        <v>1.1883541295306002</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6">
-        <v>1</v>
-      </c>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2517,28 +2492,29 @@
   <dimension ref="A1:AA11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" customWidth="1"/>
-    <col min="22" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -2741,22 +2717,22 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" t="s">
         <v>121</v>
       </c>
-      <c r="B4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
-      </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -2773,7 +2749,7 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
         <v>74</v>
@@ -2805,7 +2781,7 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -2814,15 +2790,15 @@
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F6" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" t="s">
         <v>32</v>
       </c>
       <c r="H6">
@@ -2855,7 +2831,7 @@
       <c r="T6">
         <v>1</v>
       </c>
-      <c r="Z6" s="9" t="s">
+      <c r="Z6" t="s">
         <v>58</v>
       </c>
       <c r="AA6">
@@ -2864,18 +2840,18 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
       <c r="H7">
@@ -2893,7 +2869,7 @@
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="Z7" s="9" t="s">
+      <c r="Z7" t="s">
         <v>58</v>
       </c>
       <c r="AA7">
@@ -2902,7 +2878,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -2911,15 +2887,15 @@
         <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F8" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
       <c r="H8">
@@ -2952,7 +2928,7 @@
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="Z8" s="9" t="s">
+      <c r="Z8" t="s">
         <v>58</v>
       </c>
       <c r="AA8">
@@ -2961,18 +2937,18 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" t="s">
         <v>32</v>
       </c>
       <c r="H9">
@@ -2990,7 +2966,7 @@
       <c r="T9">
         <v>1</v>
       </c>
-      <c r="Z9" s="9" t="s">
+      <c r="Z9" t="s">
         <v>58</v>
       </c>
       <c r="AA9">
@@ -2999,7 +2975,7 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
@@ -3008,15 +2984,15 @@
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" t="s">
         <v>32</v>
       </c>
       <c r="H10">
@@ -3049,7 +3025,7 @@
       <c r="T10">
         <v>1</v>
       </c>
-      <c r="Z10" s="9" t="s">
+      <c r="Z10" t="s">
         <v>58</v>
       </c>
       <c r="AA10">
@@ -3058,18 +3034,18 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" t="s">
         <v>32</v>
       </c>
       <c r="H11">
@@ -3087,7 +3063,7 @@
       <c r="T11">
         <v>1</v>
       </c>
-      <c r="Z11" s="9" t="s">
+      <c r="Z11" t="s">
         <v>58</v>
       </c>
       <c r="AA11">
@@ -3197,10 +3173,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3341,32 +3317,32 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/egasoline/Model_Data_Base_egasoline.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/egasoline/Model_Data_Base_egasoline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\egasoline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\egasoline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C16C014-E571-4F49-BE2B-DFA7AED3CBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0243637A-7801-4998-B2AF-82338479BBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-10110" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" concurrentManualCount="6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="134">
   <si>
     <t>Unit</t>
   </si>
@@ -295,12 +295,6 @@
     <t>power_wholesale</t>
   </si>
   <si>
-    <t>pl_dh</t>
-  </si>
-  <si>
-    <t>dh</t>
-  </si>
-  <si>
     <t>water</t>
   </si>
   <si>
@@ -482,9 +476,6 @@
   </si>
   <si>
     <t>excess_heat</t>
-  </si>
-  <si>
-    <t>heat</t>
   </si>
 </sst>
 </file>
@@ -1375,8 +1366,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA11" totalsRowShown="0">
-  <autoFilter ref="A1:AA11" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:AA10" totalsRowShown="0">
+  <autoFilter ref="A1:AA10" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{26B0CA71-1EA9-44CF-8E6D-31054ECA99A6}" name="Connection"/>
     <tableColumn id="26" xr3:uid="{E67F4435-EF76-417C-B715-53719E5FB41F}" name="Object_type"/>
@@ -1415,7 +1406,7 @@
   <autoFilter ref="A1:K5" xr:uid="{070C7B69-9214-47B9-93F0-C6C6118ED7CC}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{59CF1CEF-E7FA-4B7F-9443-D4A6EAAB7A8F}" name="Storage" dataDxfId="0">
-      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A100,ISNUMBER(FIND("storage",Connections!A2:A100)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Connections!A2:A99,ISNUMBER(FIND("storage",Connections!A2:A99)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{8C29206C-8DC6-44DB-A8D1-3D5625C277AD}" name="Object_type"/>
     <tableColumn id="4" xr3:uid="{AEAA1B51-84C1-491F-81D5-7757B30BDCCD}" name="value_before"/>
@@ -1740,29 +1731,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1770,7 +1761,7 @@
         <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
@@ -1779,16 +1770,16 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J1" t="s">
         <v>64</v>
@@ -1815,10 +1806,10 @@
         <v>41</v>
       </c>
       <c r="R1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1826,40 +1817,40 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -1879,28 +1870,28 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>42</v>
@@ -1909,22 +1900,22 @@
         <v>20.192799999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
@@ -1938,54 +1929,54 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
@@ -2023,22 +2014,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CABA7C5-6230-4207-9D35-0A95D86E66AC}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2052,10 +2043,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>3</v>
@@ -2064,34 +2055,34 @@
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>69</v>
       </c>
@@ -2103,7 +2094,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="7"/>
@@ -2116,9 +2107,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>62</v>
@@ -2128,7 +2119,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -2141,9 +2132,9 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -2153,7 +2144,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2166,9 +2157,9 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>60</v>
@@ -2177,15 +2168,15 @@
         <v>70</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -2201,9 +2192,9 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>25</v>
@@ -2212,12 +2203,12 @@
         <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -2234,26 +2225,26 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -2271,27 +2262,27 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -2312,23 +2303,23 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -2345,38 +2336,38 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -2391,31 +2382,31 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="6">
@@ -2436,12 +2427,12 @@
       </c>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>70</v>
@@ -2450,7 +2441,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -2489,35 +2480,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:AA11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -2600,7 +2591,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -2659,24 +2650,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
         <v>32</v>
@@ -2715,24 +2706,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" t="s">
         <v>119</v>
       </c>
-      <c r="B4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" t="s">
-        <v>121</v>
-      </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G4" t="s">
         <v>32</v>
@@ -2741,18 +2732,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>124</v>
+      </c>
+      <c r="F5" t="s">
+        <v>72</v>
       </c>
       <c r="G5" t="s">
         <v>32</v>
@@ -2763,11 +2760,26 @@
       <c r="I5">
         <v>1000</v>
       </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
       <c r="L5">
         <v>1000</v>
       </c>
       <c r="M5">
         <v>1000</v>
+      </c>
+      <c r="N5">
+        <v>1000</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -2779,24 +2791,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G6" t="s">
         <v>32</v>
@@ -2807,26 +2813,11 @@
       <c r="I6">
         <v>1000</v>
       </c>
-      <c r="J6">
-        <v>1000</v>
-      </c>
-      <c r="K6">
-        <v>1000</v>
-      </c>
       <c r="L6">
         <v>1000</v>
       </c>
       <c r="M6">
         <v>1000</v>
-      </c>
-      <c r="N6">
-        <v>1000</v>
-      </c>
-      <c r="O6">
-        <v>1000</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
       </c>
       <c r="T6">
         <v>1</v>
@@ -2838,18 +2829,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>125</v>
+      </c>
+      <c r="F7" t="s">
+        <v>72</v>
       </c>
       <c r="G7" t="s">
         <v>32</v>
@@ -2860,11 +2857,26 @@
       <c r="I7">
         <v>1000</v>
       </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
       <c r="L7">
         <v>1000</v>
       </c>
       <c r="M7">
         <v>1000</v>
+      </c>
+      <c r="N7">
+        <v>1000</v>
+      </c>
+      <c r="O7">
+        <v>1000</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
       </c>
       <c r="T7">
         <v>1</v>
@@ -2876,24 +2888,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -2904,26 +2910,11 @@
       <c r="I8">
         <v>1000</v>
       </c>
-      <c r="J8">
-        <v>1000</v>
-      </c>
-      <c r="K8">
-        <v>1000</v>
-      </c>
       <c r="L8">
         <v>1000</v>
       </c>
       <c r="M8">
         <v>1000</v>
-      </c>
-      <c r="N8">
-        <v>1000</v>
-      </c>
-      <c r="O8">
-        <v>1000</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -2935,18 +2926,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>126</v>
+      </c>
+      <c r="F9" t="s">
+        <v>72</v>
       </c>
       <c r="G9" t="s">
         <v>32</v>
@@ -2957,11 +2954,26 @@
       <c r="I9">
         <v>1000</v>
       </c>
+      <c r="J9">
+        <v>1000</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
       <c r="L9">
         <v>1000</v>
       </c>
       <c r="M9">
         <v>1000</v>
+      </c>
+      <c r="N9">
+        <v>1000</v>
+      </c>
+      <c r="O9">
+        <v>1000</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
       </c>
       <c r="T9">
         <v>1</v>
@@ -2973,24 +2985,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
         <v>32</v>
@@ -3001,26 +3007,11 @@
       <c r="I10">
         <v>1000</v>
       </c>
-      <c r="J10">
-        <v>1000</v>
-      </c>
-      <c r="K10">
-        <v>1000</v>
-      </c>
       <c r="L10">
         <v>1000</v>
       </c>
       <c r="M10">
         <v>1000</v>
-      </c>
-      <c r="N10">
-        <v>1000</v>
-      </c>
-      <c r="O10">
-        <v>1000</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -3029,44 +3020,6 @@
         <v>58</v>
       </c>
       <c r="AA10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11">
-        <v>1000</v>
-      </c>
-      <c r="I11">
-        <v>1000</v>
-      </c>
-      <c r="L11">
-        <v>1000</v>
-      </c>
-      <c r="M11">
-        <v>1000</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA11">
         <v>1</v>
       </c>
     </row>
@@ -3084,7 +3037,7 @@
           <x14:formula1>
             <xm:f>Drop_Down!$A$2:$A$60</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B100</xm:sqref>
+          <xm:sqref>B2:B99</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3095,22 +3048,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -3145,9 +3098,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3171,12 +3124,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3220,129 +3173,129 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DC79B9-9C58-497E-9FD8-D3F2239E9BDC}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
